--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>мердж</t>
   </si>
@@ -28,9 +28,6 @@
     <t>объеденять можно только сквинки одного уровня - это объединение создает сквинки следующего уровня если он доступен</t>
   </si>
   <si>
-    <t>если сквинки следующего уровня не доступен - то объеденять максимальные уровни нельзя</t>
-  </si>
-  <si>
     <t>у каждого сквинки свой биом</t>
   </si>
   <si>
@@ -40,28 +37,106 @@
     <t>если сквинки переместить в чужой биом - сияние исчезнет</t>
   </si>
   <si>
-    <t>объединение сияющих скинки - дает игровую валюту - сияние</t>
-  </si>
-  <si>
-    <t>за сияние (игровые деньги) в МАГАЗИН е можно купить бусты</t>
-  </si>
-  <si>
-    <t>БУСТЫ:</t>
-  </si>
-  <si>
-    <t>кисть - меняет выбранный биом</t>
-  </si>
-  <si>
-    <t>следующий по уровню сквинки</t>
-  </si>
-  <si>
     <t>ЦЕЛИ:</t>
   </si>
   <si>
-    <t>ключ - освобождает заблокированный на поле биом</t>
-  </si>
-  <si>
-    <t>очистить уровень - есть КАМНИ которые очищаются при слиянии сквинки на соседних клетках</t>
+    <t>если сквинки следующего уровня не доступен - то объединенные сквинки исчезают (очистка поля) и дают + 2 СИЯНИЯ</t>
+  </si>
+  <si>
+    <t>СИЯНИЕ - награда/очки/игровая валюта</t>
+  </si>
+  <si>
+    <t>объединение ОБЫЧНЫЙ + ОБЫЧНЫЙ = 1 СИЯНИЕ</t>
+  </si>
+  <si>
+    <t>объединение СИЯЮЩИЙ + ОБЫЧНЫЙ = 2 СИЯНИЕ</t>
+  </si>
+  <si>
+    <t>объединение СИЯЮЩИЙ +СИЯЮЩИЙ = 3 СИЯНИЕ</t>
+  </si>
+  <si>
+    <t>МАГИЯ - случается при накоплении 10 СИЯНИЯ</t>
+  </si>
+  <si>
+    <t>если есть на поле ЗАМОК (заблокированный биом) СИЯНИЕ -=10, ЗАМОК убирается с поля, биом становится доступным</t>
+  </si>
+  <si>
+    <t>если есть на поле ГРОЗА (заблокированный биом) СИЯНИЕ -=10, ГРОЗА убирается с поля, биом становится доступным</t>
+  </si>
+  <si>
+    <t>БЛОКИРОВКА - биом (клетка) может быть заблокирована замком или тучами (гразой)</t>
+  </si>
+  <si>
+    <t>замок - нельзя убрать ничем кроми МАГИИ</t>
+  </si>
+  <si>
+    <t>ТУЧТ - если рядом смерджить сквинки - исчезнут, если за 2 хода не исчезли - превращаются в ГРОЗА</t>
+  </si>
+  <si>
+    <t>ГРОЗА -  если рядом смерджить сквинки - превращаются обратно в ТУЧИ (есть снова 2 хода на очистку)</t>
+  </si>
+  <si>
+    <t>если есть на поле ТУЧИ (заблокированный биом) СИЯНИЕ -=10, ТУЧИ убираются с поля, биом становится доступным</t>
+  </si>
+  <si>
+    <t>ДРАКОН - появявляется в случайной свободной клетке (биоме), всегда сияющий сквинки, мерджится со сквинки любого уровня (джокер)</t>
+  </si>
+  <si>
+    <t>Открой нового сквинки (до мерджить до состояния выхода сквинки нового уровня) - как появился - сквинки летит в коллекцию, уровень пройден</t>
+  </si>
+  <si>
+    <t>Очистить карту от замков</t>
+  </si>
+  <si>
+    <t>Очистить карту от туч/гроз</t>
+  </si>
+  <si>
+    <t>Набрать N сияния</t>
+  </si>
+  <si>
+    <t>Получить N ДРАКОНОВ</t>
+  </si>
+  <si>
+    <t>СРОЧНОЕ - все 5 типов но с ограничением числа ходов</t>
+  </si>
+  <si>
+    <t>КАРТА</t>
+  </si>
+  <si>
+    <t>на глобальной карте есть ТОЧКИ</t>
+  </si>
+  <si>
+    <t>в нутри точки есть карточки уровней от 1 до 3</t>
+  </si>
+  <si>
+    <t>за каждую пройденную карточку игрок получает нового сквинки</t>
+  </si>
+  <si>
+    <t>некоторые точки за прохождение всех карточек дают доп. (или несколько доп.) сквинки (подарок или несколько подарков возле точке)</t>
+  </si>
+  <si>
+    <t>Игрок может в ТОЧКЕ пройти только 1 карточку что бы идти дальше</t>
+  </si>
+  <si>
+    <t>ЧТО ЭТО ДАСТ</t>
+  </si>
+  <si>
+    <t>потеря части коллекции (получит меньше сквинки)</t>
+  </si>
+  <si>
+    <t>игрок сам регулирует сложность - больше колекция - сложнее играть</t>
+  </si>
+  <si>
+    <t>НАГРАДА ЗА ТОЧКУ</t>
+  </si>
+  <si>
+    <t>1 * - прохождение одной из карточек (до мерджить до состояния точка)</t>
+  </si>
+  <si>
+    <t>2 * - прохождение всех карточек в ТОЧКЕ</t>
+  </si>
+  <si>
+    <t>3 * - прохождение всех карточек в ТОЧКЕ с ПОЛНОЙ КОЛЕКЦИЕЙ СКВИНКИ (очень сложно)</t>
   </si>
 </sst>
 </file>
@@ -403,79 +478,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>9</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C47" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C48" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="игра" sheetId="1" r:id="rId1"/>
+    <sheet name="уровни" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>мердж</t>
   </si>
@@ -137,6 +138,30 @@
   </si>
   <si>
     <t>3 * - прохождение всех карточек в ТОЧКЕ с ПОЛНОЙ КОЛЕКЦИЕЙ СКВИНКИ (очень сложно)</t>
+  </si>
+  <si>
+    <t>LEVEL</t>
+  </si>
+  <si>
+    <t>squinki</t>
+  </si>
+  <si>
+    <t>squinki+t</t>
+  </si>
+  <si>
+    <t>locks</t>
+  </si>
+  <si>
+    <t>locks+t</t>
+  </si>
+  <si>
+    <t>clouds</t>
+  </si>
+  <si>
+    <t>clouds+t</t>
+  </si>
+  <si>
+    <t>add Squinki</t>
   </si>
 </sst>
 </file>
@@ -152,12 +177,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -172,8 +209,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -681,4 +721,781 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="14.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="игра" sheetId="1" r:id="rId1"/>
     <sheet name="уровни" sheetId="2" r:id="rId2"/>
+    <sheet name="мердж" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>мердж</t>
   </si>
@@ -162,18 +163,180 @@
   </si>
   <si>
     <t>add Squinki</t>
+  </si>
+  <si>
+    <t>уровень</t>
+  </si>
+  <si>
+    <t>сколько какого уровня сквинки надо, для получения уровня в 1й колонке</t>
+  </si>
+  <si>
+    <t>ур 1</t>
+  </si>
+  <si>
+    <t>ур 2</t>
+  </si>
+  <si>
+    <t>ур 3</t>
+  </si>
+  <si>
+    <t>ур 4</t>
+  </si>
+  <si>
+    <t>ур 5</t>
+  </si>
+  <si>
+    <t>ур 6</t>
+  </si>
+  <si>
+    <t>ур 7</t>
+  </si>
+  <si>
+    <t>ур 8</t>
+  </si>
+  <si>
+    <t>ур 9</t>
+  </si>
+  <si>
+    <t>ур 10</t>
+  </si>
+  <si>
+    <t>ур 11</t>
+  </si>
+  <si>
+    <t>ур 12</t>
+  </si>
+  <si>
+    <t>ур 13</t>
+  </si>
+  <si>
+    <t>ур 14</t>
+  </si>
+  <si>
+    <t>ур 15</t>
+  </si>
+  <si>
+    <t>ур 16</t>
+  </si>
+  <si>
+    <t>ур 17</t>
+  </si>
+  <si>
+    <t>ур 18</t>
+  </si>
+  <si>
+    <t>ур 19</t>
+  </si>
+  <si>
+    <t>ур 20</t>
+  </si>
+  <si>
+    <t>ур 21</t>
+  </si>
+  <si>
+    <t>ур 22</t>
+  </si>
+  <si>
+    <t>ур 23</t>
+  </si>
+  <si>
+    <t>ур 24</t>
+  </si>
+  <si>
+    <t>ур 25</t>
+  </si>
+  <si>
+    <t>ур 26</t>
+  </si>
+  <si>
+    <t>ур 27</t>
+  </si>
+  <si>
+    <t>ур 28</t>
+  </si>
+  <si>
+    <t>ур 29</t>
+  </si>
+  <si>
+    <t>ур 30</t>
+  </si>
+  <si>
+    <t>ур 31</t>
+  </si>
+  <si>
+    <t>ур 32</t>
+  </si>
+  <si>
+    <t>ур 33</t>
+  </si>
+  <si>
+    <t>ур 34</t>
+  </si>
+  <si>
+    <t>ур 35</t>
+  </si>
+  <si>
+    <t>ур 36</t>
+  </si>
+  <si>
+    <t>ур 37</t>
+  </si>
+  <si>
+    <t>ур 38</t>
+  </si>
+  <si>
+    <t>ур 39</t>
+  </si>
+  <si>
+    <t>ур 40</t>
+  </si>
+  <si>
+    <t>ур 41</t>
+  </si>
+  <si>
+    <t>ур 42</t>
+  </si>
+  <si>
+    <t>ур 43</t>
+  </si>
+  <si>
+    <t>ур 44</t>
+  </si>
+  <si>
+    <t>ур 45</t>
+  </si>
+  <si>
+    <t>ур 46</t>
+  </si>
+  <si>
+    <t>ур 47</t>
+  </si>
+  <si>
+    <t>ур 48</t>
+  </si>
+  <si>
+    <t>ур 49</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -209,11 +372,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1498,4 +1662,575 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AX52"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="50" width="5.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" t="s">
+        <v>62</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" t="s">
+        <v>67</v>
+      </c>
+      <c r="S2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U2" t="s">
+        <v>70</v>
+      </c>
+      <c r="V2" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" t="s">
+        <v>72</v>
+      </c>
+      <c r="X2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>59.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>64.599999999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>72.400000000000006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>80.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>85.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>90.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>95.8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>98.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>103.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>108.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>111.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>116.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>119.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>121.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>124.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="игра" sheetId="1" r:id="rId1"/>
-    <sheet name="уровни" sheetId="2" r:id="rId2"/>
-    <sheet name="мердж" sheetId="3" r:id="rId3"/>
+    <sheet name="локации" sheetId="4" r:id="rId2"/>
+    <sheet name="уровни" sheetId="2" r:id="rId3"/>
+    <sheet name="мердж" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="144">
   <si>
     <t>мердж</t>
   </si>
@@ -316,13 +317,145 @@
   </si>
   <si>
     <t>ур 49</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>point 1</t>
+  </si>
+  <si>
+    <t>point 2</t>
+  </si>
+  <si>
+    <t>point 3</t>
+  </si>
+  <si>
+    <t>point 4</t>
+  </si>
+  <si>
+    <t>point 5</t>
+  </si>
+  <si>
+    <t>point 6</t>
+  </si>
+  <si>
+    <t>point 7</t>
+  </si>
+  <si>
+    <t>point 8</t>
+  </si>
+  <si>
+    <t>point 9</t>
+  </si>
+  <si>
+    <t>point 10</t>
+  </si>
+  <si>
+    <t>point 11</t>
+  </si>
+  <si>
+    <t>point 12</t>
+  </si>
+  <si>
+    <t>point 13</t>
+  </si>
+  <si>
+    <t>point 14</t>
+  </si>
+  <si>
+    <t>point 15</t>
+  </si>
+  <si>
+    <t>point 16</t>
+  </si>
+  <si>
+    <t>point 17</t>
+  </si>
+  <si>
+    <t>point 18</t>
+  </si>
+  <si>
+    <t>point 19</t>
+  </si>
+  <si>
+    <t>point 20</t>
+  </si>
+  <si>
+    <t>point 21</t>
+  </si>
+  <si>
+    <t>point 22</t>
+  </si>
+  <si>
+    <t>POINT #</t>
+  </si>
+  <si>
+    <t>TASK 1</t>
+  </si>
+  <si>
+    <t>TASK 2</t>
+  </si>
+  <si>
+    <t>TASK 3</t>
+  </si>
+  <si>
+    <t>начальный</t>
+  </si>
+  <si>
+    <t>в каждой</t>
+  </si>
+  <si>
+    <t>за поинты</t>
+  </si>
+  <si>
+    <t>доп</t>
+  </si>
+  <si>
+    <t>и того</t>
+  </si>
+  <si>
+    <t>NEW T</t>
+  </si>
+  <si>
+    <t>LOCK</t>
+  </si>
+  <si>
+    <t>LOCK T</t>
+  </si>
+  <si>
+    <t>CLOUD</t>
+  </si>
+  <si>
+    <t>CLOUD T</t>
+  </si>
+  <si>
+    <t>min level</t>
+  </si>
+  <si>
+    <t>игрок игнорирует NEW и не проходит полностью локации</t>
+  </si>
+  <si>
+    <t>mid level</t>
+  </si>
+  <si>
+    <t>игрок собирает максимум NEW но не проходит полностью локации</t>
+  </si>
+  <si>
+    <t>max level</t>
+  </si>
+  <si>
+    <t>игрок собирает максимум NEW и проходит полностью локации</t>
+  </si>
+  <si>
+    <t>С ЧЕМ ИГРОК ПРИХОДИТ В НОВЫЙ ПОИНТ:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,8 +472,18 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,6 +502,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -372,12 +521,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -889,6 +1053,615 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="4" width="8.88671875" style="6"/>
+    <col min="5" max="5" width="9.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="6"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="9">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L2" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" t="s">
+        <v>130</v>
+      </c>
+      <c r="N2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="9">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9">
+        <v>3</v>
+      </c>
+      <c r="G3" s="9">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>22</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <f>J3+K3+L3+M3</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>6</v>
+      </c>
+      <c r="G5" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="6">
+        <v>6</v>
+      </c>
+      <c r="F6" s="6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>9</v>
+      </c>
+      <c r="G7" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="6">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6">
+        <v>10</v>
+      </c>
+      <c r="G8" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E9" s="6">
+        <v>6</v>
+      </c>
+      <c r="F9" s="6">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="6">
+        <v>6</v>
+      </c>
+      <c r="F10" s="6">
+        <v>12</v>
+      </c>
+      <c r="G10" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="6">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E12" s="6">
+        <v>6</v>
+      </c>
+      <c r="F12" s="6">
+        <v>14</v>
+      </c>
+      <c r="G12" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="6">
+        <v>6</v>
+      </c>
+      <c r="F13" s="6">
+        <v>15</v>
+      </c>
+      <c r="G13" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" s="6">
+        <v>6</v>
+      </c>
+      <c r="F14" s="6">
+        <v>16</v>
+      </c>
+      <c r="G14" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="6">
+        <v>6</v>
+      </c>
+      <c r="F15" s="6">
+        <v>17</v>
+      </c>
+      <c r="G15" s="6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="6">
+        <v>6</v>
+      </c>
+      <c r="F16" s="6">
+        <v>18</v>
+      </c>
+      <c r="G16" s="6">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="6">
+        <v>6</v>
+      </c>
+      <c r="F17" s="6">
+        <v>19</v>
+      </c>
+      <c r="G17" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="6">
+        <v>6</v>
+      </c>
+      <c r="F18" s="6">
+        <v>20</v>
+      </c>
+      <c r="G18" s="6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" s="6">
+        <v>6</v>
+      </c>
+      <c r="F19" s="6">
+        <v>21</v>
+      </c>
+      <c r="G19" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="6">
+        <v>6</v>
+      </c>
+      <c r="F20" s="6">
+        <v>22</v>
+      </c>
+      <c r="G20" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="6">
+        <v>6</v>
+      </c>
+      <c r="F21" s="6">
+        <v>23</v>
+      </c>
+      <c r="G21" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="6">
+        <v>6</v>
+      </c>
+      <c r="F22" s="6">
+        <v>24</v>
+      </c>
+      <c r="G22" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="6">
+        <v>6</v>
+      </c>
+      <c r="F23" s="6">
+        <v>25</v>
+      </c>
+      <c r="G23" s="6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1664,7 +2437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AX52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="151">
   <si>
     <t>мердж</t>
   </si>
@@ -449,6 +449,27 @@
   </si>
   <si>
     <t>С ЧЕМ ИГРОК ПРИХОДИТ В НОВЫЙ ПОИНТ:</t>
+  </si>
+  <si>
+    <t>УРОВЕНЬ</t>
+  </si>
+  <si>
+    <t>РЕЗУЛЬТАТ</t>
+  </si>
+  <si>
+    <t>СКВИНКИ</t>
+  </si>
+  <si>
+    <t>ЧИСЛО, шт</t>
+  </si>
+  <si>
+    <t>макс уровень</t>
+  </si>
+  <si>
+    <t>ОСТАТОК, шт</t>
+  </si>
+  <si>
+    <t>начального уровня</t>
   </si>
 </sst>
 </file>
@@ -509,7 +530,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -517,11 +538,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -540,6 +576,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1060,8 +1105,10 @@
     <col min="5" max="5" width="9.6640625" style="6" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" style="6" customWidth="1"/>
     <col min="7" max="8" width="8.88671875" style="6"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="12" max="12" width="10.21875" customWidth="1"/>
+    <col min="10" max="11" width="11.33203125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="13" style="6" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1110,19 +1157,19 @@
       <c r="G2" s="9">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="6" t="s">
         <v>131</v>
       </c>
     </row>
@@ -1148,159 +1195,207 @@
       <c r="G3" s="9">
         <v>5</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
         <v>22</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="6">
         <v>22</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="6">
         <v>5</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="6">
         <f>J3+K3+L3+M3</f>
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="9">
         <v>3</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="9">
         <v>4</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="9">
         <v>4</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="9">
         <v>6</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="9">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <v>6</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="12">
         <v>8</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="12">
         <v>14</v>
       </c>
+      <c r="J6" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>6</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="12">
         <v>9</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="12">
         <v>16</v>
       </c>
+      <c r="J7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="12">
         <v>6</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="12">
         <v>10</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="12">
         <v>18</v>
       </c>
+      <c r="J8" s="11">
+        <v>1</v>
+      </c>
+      <c r="K8" s="11">
+        <v>15</v>
+      </c>
+      <c r="L8" s="11">
+        <f>J8 + INT(LOG(K8,2))</f>
+        <v>4</v>
+      </c>
+      <c r="M8" s="11">
+        <f>K8 - 2^INT(LOG(K8,2))</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="12">
         <v>6</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="12">
         <v>11</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="12">
         <v>20</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11" t="e">
+        <f t="shared" ref="L9:L20" si="0">J9 + INT(LOG(K9,2))</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="M9" s="11" t="e">
+        <f t="shared" ref="M9:M21" si="1">K9 - 2^INT(LOG(K9,2))</f>
+        <v>#NUM!</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1325,6 +1420,16 @@
       <c r="G10" s="6">
         <v>22</v>
       </c>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M10" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
@@ -1348,6 +1453,16 @@
       <c r="G11" s="6">
         <v>24</v>
       </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M11" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -1371,6 +1486,16 @@
       <c r="G12" s="6">
         <v>26</v>
       </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M12" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
@@ -1394,6 +1519,16 @@
       <c r="G13" s="6">
         <v>28</v>
       </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M13" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
@@ -1417,6 +1552,16 @@
       <c r="G14" s="6">
         <v>30</v>
       </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M14" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -1440,6 +1585,16 @@
       <c r="G15" s="6">
         <v>32</v>
       </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M15" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -1463,8 +1618,18 @@
       <c r="G16" s="6">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M16" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>116</v>
       </c>
@@ -1486,8 +1651,18 @@
       <c r="G17" s="6">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M17" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>117</v>
       </c>
@@ -1509,8 +1684,18 @@
       <c r="G18" s="6">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M18" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>118</v>
       </c>
@@ -1532,8 +1717,18 @@
       <c r="G19" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M19" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>119</v>
       </c>
@@ -1555,8 +1750,18 @@
       <c r="G20" s="6">
         <v>42</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="M20" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>120</v>
       </c>
@@ -1578,8 +1783,18 @@
       <c r="G21" s="6">
         <v>44</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11" t="e">
+        <f>J21 + INT(LOG(K21,2))</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="M21" s="11" t="e">
+        <f t="shared" si="1"/>
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>121</v>
       </c>
@@ -1602,7 +1817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>122</v>
       </c>
@@ -1625,12 +1840,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>137</v>
       </c>
@@ -1638,7 +1853,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>139</v>
       </c>
@@ -1646,7 +1861,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>141</v>
       </c>

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -476,7 +476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +501,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -557,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -585,6 +592,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1098,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="8.88671875" style="6"/>
@@ -1111,7 +1121,7 @@
     <col min="14" max="14" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>123</v>
       </c>
@@ -1135,7 +1145,7 @@
       </c>
       <c r="H1" s="5"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
         <v>101</v>
       </c>
@@ -1173,7 +1183,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>102</v>
       </c>
@@ -1212,7 +1222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>103</v>
       </c>
@@ -1235,7 +1245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>104</v>
       </c>
@@ -1258,7 +1268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>105</v>
       </c>
@@ -1293,7 +1303,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>106</v>
       </c>
@@ -1328,7 +1338,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>107</v>
       </c>
@@ -1354,18 +1364,21 @@
         <v>1</v>
       </c>
       <c r="K8" s="11">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L8" s="11">
         <f>J8 + INT(LOG(K8,2))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8" s="11">
         <f>K8 - 2^INT(LOG(K8,2))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="O8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>108</v>
       </c>
@@ -1387,52 +1400,66 @@
       <c r="G9" s="12">
         <v>20</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11" t="e">
+      <c r="J9" s="11">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11">
+        <v>12</v>
+      </c>
+      <c r="L9" s="11">
         <f t="shared" ref="L9:L20" si="0">J9 + INT(LOG(K9,2))</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="M9" s="11" t="e">
+        <v>4</v>
+      </c>
+      <c r="M9" s="11">
         <f t="shared" ref="M9:M21" si="1">K9 - 2^INT(LOG(K9,2))</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="12">
         <v>6</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="12">
         <v>12</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="12">
         <v>22</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11" t="e">
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11">
+        <v>4</v>
+      </c>
+      <c r="L10" s="11">
         <f t="shared" si="0"/>
-        <v>#NUM!</v>
-      </c>
-      <c r="M10" s="11" t="e">
+        <v>3</v>
+      </c>
+      <c r="M10" s="11">
         <f t="shared" si="1"/>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>110</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1441,7 +1468,7 @@
       <c r="C11" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="13" t="s">
         <v>134</v>
       </c>
       <c r="E11" s="6">
@@ -1464,7 +1491,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>111</v>
       </c>
@@ -1497,7 +1524,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>112</v>
       </c>
@@ -1530,7 +1557,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>113</v>
       </c>
@@ -1563,7 +1590,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>114</v>
       </c>
@@ -1596,7 +1623,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>115</v>
       </c>

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -505,7 +505,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1462,22 +1461,22 @@
       <c r="A11" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="12" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="12">
         <v>6</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="12">
         <v>13</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="12">
         <v>24</v>
       </c>
       <c r="J11" s="11"/>
@@ -1492,25 +1491,25 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="12">
         <v>6</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="12">
         <v>14</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="12">
         <v>26</v>
       </c>
       <c r="J12" s="11"/>
@@ -1531,7 +1530,7 @@
       <c r="B13" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="12" t="s">
         <v>136</v>
       </c>
       <c r="D13" s="6" t="s">

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -1360,10 +1360,10 @@
         <v>18</v>
       </c>
       <c r="J8" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" s="11">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="L8" s="11">
         <f>J8 + INT(LOG(K8,2))</f>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="M8" s="11">
         <f>K8 - 2^INT(LOG(K8,2))</f>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1524,25 +1524,25 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="12">
         <v>6</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="12">
         <v>15</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="12">
         <v>28</v>
       </c>
       <c r="J13" s="11"/>
@@ -1557,25 +1557,25 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="12">
         <v>6</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="12">
         <v>16</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="12">
         <v>30</v>
       </c>
       <c r="J14" s="11"/>
@@ -1590,25 +1590,25 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="12">
         <v>6</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="12">
         <v>17</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="12">
         <v>32</v>
       </c>
       <c r="J15" s="11"/>
@@ -1623,25 +1623,25 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="12">
         <v>6</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="12">
         <v>18</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="12">
         <v>34</v>
       </c>
       <c r="J16" s="11"/>

--- a/_SRC_/механики.xlsx
+++ b/_SRC_/механики.xlsx
@@ -1656,25 +1656,25 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="12">
         <v>6</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="12">
         <v>19</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="12">
         <v>36</v>
       </c>
       <c r="J17" s="11"/>
@@ -1689,25 +1689,25 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="12">
         <v>6</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="12">
         <v>20</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="12">
         <v>38</v>
       </c>
       <c r="J18" s="11"/>
